--- a/game_config/Datas/BuffConfig.xlsx
+++ b/game_config/Datas/BuffConfig.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\temp\codex-buff-config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7F8B3E-9EDF-403E-85C6-2ED9521B85FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DCC34E-572C-4CF3-9169-D3252798A64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuffConfig" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="103">
   <si>
     <t>##var</t>
   </si>
@@ -117,9 +117,6 @@
     <t>持续恢复</t>
   </si>
   <si>
-    <t>1,50</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
@@ -264,9 +261,6 @@
     <t>Source</t>
   </si>
   <si>
-    <t>1,-5</t>
-  </si>
-  <si>
     <t>4003</t>
   </si>
   <si>
@@ -316,6 +310,42 @@
   </si>
   <si>
     <t>10002,-500</t>
+  </si>
+  <si>
+    <t>5,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeNumeric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegisterDamageAbsorber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DealDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -684,21 +714,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" customWidth="1"/>
-    <col min="4" max="4" width="64.77734375" customWidth="1"/>
-    <col min="5" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="11" width="16.77734375" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" customWidth="1"/>
-    <col min="13" max="13" width="20.77734375" customWidth="1"/>
-    <col min="14" max="19" width="16.77734375" customWidth="1"/>
+    <col min="1" max="1" width="9.75" customWidth="1"/>
+    <col min="2" max="2" width="10.75" customWidth="1"/>
+    <col min="3" max="3" width="16.75" customWidth="1"/>
+    <col min="4" max="4" width="64.75" customWidth="1"/>
+    <col min="5" max="6" width="16.75" customWidth="1"/>
+    <col min="7" max="9" width="18.75" customWidth="1"/>
+    <col min="10" max="11" width="16.75" customWidth="1"/>
+    <col min="12" max="12" width="18.75" customWidth="1"/>
+    <col min="13" max="13" width="20.75" customWidth="1"/>
+    <col min="14" max="19" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="27" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -709,7 +739,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -718,25 +748,25 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>5</v>
@@ -757,7 +787,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="27" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -780,43 +810,43 @@
         <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -827,7 +857,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -836,25 +866,25 @@
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>16</v>
@@ -875,7 +905,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -886,7 +916,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>20</v>
@@ -895,25 +925,25 @@
         <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>22</v>
@@ -934,358 +964,358 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="L10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="N10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="P10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="S10" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/game_config/Datas/BuffConfig.xlsx
+++ b/game_config/Datas/BuffConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DCC34E-572C-4CF3-9169-D3252798A64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472D04CF-8A35-4571-AE7A-CE87500B1208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuffConfig" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="109">
   <si>
     <t>##var</t>
   </si>
@@ -345,6 +345,30 @@
   </si>
   <si>
     <t>DealDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复技能添加的持续恢复效果：持续24秒，每3秒恢复10点生命，共8次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Refresh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeepCadence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Keep</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -713,22 +737,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.75" customWidth="1"/>
-    <col min="2" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="16.75" customWidth="1"/>
-    <col min="4" max="4" width="64.75" customWidth="1"/>
-    <col min="5" max="6" width="16.75" customWidth="1"/>
-    <col min="7" max="9" width="18.75" customWidth="1"/>
-    <col min="10" max="11" width="16.75" customWidth="1"/>
-    <col min="12" max="12" width="18.75" customWidth="1"/>
-    <col min="13" max="13" width="20.75" customWidth="1"/>
-    <col min="14" max="19" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
+    <col min="4" max="4" width="64.77734375" customWidth="1"/>
+    <col min="5" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="9" width="18.77734375" customWidth="1"/>
+    <col min="10" max="11" width="16.77734375" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="13" max="13" width="20.77734375" customWidth="1"/>
+    <col min="14" max="19" width="16.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -787,7 +811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="27" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -846,7 +870,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -905,7 +929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -964,7 +988,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>51</v>
       </c>
@@ -1023,7 +1047,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>51</v>
       </c>
@@ -1082,7 +1106,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>51</v>
       </c>
@@ -1141,7 +1165,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>51</v>
       </c>
@@ -1200,7 +1224,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>51</v>
       </c>
@@ -1259,7 +1283,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>51</v>
       </c>
@@ -1317,6 +1341,61 @@
       <c r="S10" s="2" t="s">
         <v>93</v>
       </c>
+    </row>
+    <row r="11" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2002</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="2">
+        <v>24</v>
+      </c>
+      <c r="F11" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2002</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>10</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S11" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
